--- a/form-control-tests.xlsx
+++ b/form-control-tests.xlsx
@@ -1,26 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10914"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/russweakley-intopia/Desktop/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{731996E3-E473-284D-B24C-7D18828E652F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <bookViews>
-    <workbookView xWindow="19880" yWindow="2260" windowWidth="15960" windowHeight="18080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="40" windowWidth="15960" windowHeight="18080"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet 1-1" sheetId="1" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="34">
   <si>
     <t>Raw</t>
   </si>
@@ -55,6 +46,9 @@
     <t>&lt;select&gt;</t>
   </si>
   <si>
+    <t>Yes for all. No for Firefox Windows</t>
+  </si>
+  <si>
     <t>&lt;input type="button"&gt;</t>
   </si>
   <si>
@@ -77,6 +71,9 @@
   </si>
   <si>
     <t>&lt;input type="image"&gt;</t>
+  </si>
+  <si>
+    <t>No for all. Red for Chrome and Firefox  Windows</t>
   </si>
   <si>
     <t>&lt;input type="month"&gt;</t>
@@ -121,15 +118,23 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="0" formatCode="General"/>
+  </numFmts>
+  <fonts count="3">
     <font>
       <sz val="10"/>
       <color indexed="8"/>
       <name val="Helvetica Neue"/>
     </font>
     <font>
-      <b/>
+      <sz val="12"/>
+      <color indexed="8"/>
+      <name val="Helvetica Neue"/>
+    </font>
+    <font>
+      <b val="1"/>
       <sz val="10"/>
       <color indexed="8"/>
       <name val="Helvetica Neue"/>
@@ -210,39 +215,39 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="10">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1">
+    <xf numFmtId="49" fontId="0" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
+    <xf numFmtId="49" fontId="0" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -253,85 +258,26 @@
   <tableStyles count="0"/>
   <colors>
     <indexedColors>
-      <rgbColor rgb="FF000000"/>
-      <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFFF0000"/>
-      <rgbColor rgb="FF00FF00"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF000000"/>
-      <rgbColor rgb="FFBDC0BF"/>
-      <rgbColor rgb="FFA5A5A5"/>
-      <rgbColor rgb="FF3F3F3F"/>
-      <rgbColor rgb="FFFF94CA"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
+      <rgbColor rgb="ff000000"/>
+      <rgbColor rgb="ffffffff"/>
+      <rgbColor rgb="ffff0000"/>
+      <rgbColor rgb="ff00ff00"/>
+      <rgbColor rgb="ff0000ff"/>
+      <rgbColor rgb="ffffff00"/>
+      <rgbColor rgb="ffff00ff"/>
+      <rgbColor rgb="ff00ffff"/>
+      <rgbColor rgb="ff000000"/>
+      <rgbColor rgb="ffbdc0bf"/>
+      <rgbColor rgb="ffa5a5a5"/>
+      <rgbColor rgb="ff3f3f3f"/>
+      <rgbColor rgb="ffff94ca"/>
     </indexedColors>
   </colors>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Blank">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Blank">
   <a:themeElements>
     <a:clrScheme name="Blank">
       <a:dk1>
@@ -530,7 +476,7 @@
         <a:effectLst/>
         <a:sp3d/>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="50800" tIns="50800" rIns="50800" bIns="50800" numCol="1" spcCol="38100" rtlCol="0" anchor="ctr">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="50800" tIns="50800" rIns="50800" bIns="50800" numCol="1" spcCol="38100" rtlCol="0" anchor="ctr" upright="0">
         <a:spAutoFit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -548,7 +494,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1200" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1200" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -577,7 +523,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -602,7 +548,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -627,7 +573,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -652,7 +598,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -677,7 +623,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -702,7 +648,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -727,7 +673,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -752,7 +698,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -777,7 +723,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -790,15 +736,9 @@
         </a:lvl9pPr>
       </a:lstStyle>
       <a:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
         <a:fontRef idx="none"/>
       </a:style>
     </a:spDef>
@@ -815,7 +755,7 @@
         <a:effectLst/>
         <a:sp3d/>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="91439" tIns="45719" rIns="91439" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="t">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="91439" tIns="45719" rIns="91439" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="t" upright="0">
         <a:noAutofit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -833,7 +773,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -858,7 +798,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -883,7 +823,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -908,7 +848,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -933,7 +873,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -958,7 +898,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -983,7 +923,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1008,7 +948,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1033,7 +973,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1058,7 +998,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1071,15 +1011,9 @@
         </a:lvl9pPr>
       </a:lstStyle>
       <a:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
         <a:fontRef idx="none"/>
       </a:style>
     </a:lnDef>
@@ -1093,7 +1027,7 @@
         <a:effectLst/>
         <a:sp3d/>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="50800" tIns="50800" rIns="50800" bIns="50800" numCol="1" spcCol="38100" rtlCol="0" anchor="t">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="50800" tIns="50800" rIns="50800" bIns="50800" numCol="1" spcCol="38100" rtlCol="0" anchor="t" upright="0">
         <a:spAutoFit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -1111,7 +1045,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1100" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1100" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1140,7 +1074,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1165,7 +1099,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1190,7 +1124,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1215,7 +1149,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1240,7 +1174,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1265,7 +1199,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1290,7 +1224,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1315,7 +1249,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1340,7 +1274,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1353,630 +1287,624 @@
         </a:lvl9pPr>
       </a:lstStyle>
       <a:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
         <a:fontRef idx="none"/>
       </a:style>
     </a:txDef>
   </a:objectDefaults>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:G26"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="16.33203125" defaultRowHeight="20" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="16.3333" defaultRowHeight="19.9" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="31.5" style="1" customWidth="1"/>
-    <col min="2" max="8" width="16.33203125" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="16.33203125" style="1"/>
+    <col min="1" max="1" width="31.5625" style="1" customWidth="1"/>
+    <col min="2" max="6" width="16.3516" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.1875" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="16.3516" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" ht="20.05" customHeight="1">
       <c r="A1" s="2"/>
-      <c r="B1" s="3" t="s">
+      <c r="B1" t="s" s="3">
         <v>0</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" t="s" s="3">
         <v>0</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" t="s" s="3">
         <v>1</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" t="s" s="3">
         <v>1</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" t="s" s="3">
         <v>2</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" t="s" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="32.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" ht="32.25" customHeight="1">
       <c r="A2" s="4"/>
-      <c r="B2" s="5" t="s">
+      <c r="B2" t="s" s="5">
         <v>3</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" t="s" s="5">
         <v>4</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" t="s" s="5">
         <v>3</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" t="s" s="5">
         <v>4</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" t="s" s="5">
         <v>3</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" t="s" s="5">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="6" t="s">
+    <row r="3" ht="20.25" customHeight="1">
+      <c r="A3" t="s" s="6">
         <v>5</v>
       </c>
-      <c r="B3" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="8" t="s">
+      <c r="B3" t="s" s="6">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s" s="7">
+        <v>7</v>
+      </c>
+      <c r="D3" t="s" s="6">
+        <v>8</v>
+      </c>
+      <c r="E3" t="s" s="7">
+        <v>7</v>
+      </c>
+      <c r="F3" t="s" s="6">
+        <v>8</v>
+      </c>
+      <c r="G3" t="s" s="6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" ht="20.05" customHeight="1">
+      <c r="A4" t="s" s="8">
         <v>9</v>
       </c>
-      <c r="B4" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="G4" s="8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="8" t="s">
+      <c r="B4" t="s" s="8">
+        <v>6</v>
+      </c>
+      <c r="C4" t="s" s="8">
+        <v>6</v>
+      </c>
+      <c r="D4" t="s" s="8">
+        <v>8</v>
+      </c>
+      <c r="E4" t="s" s="8">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s" s="8">
+        <v>8</v>
+      </c>
+      <c r="G4" t="s" s="8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" ht="32.05" customHeight="1">
+      <c r="A5" t="s" s="8">
         <v>10</v>
       </c>
-      <c r="B5" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="G5" s="8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="8" t="s">
+      <c r="B5" t="s" s="8">
+        <v>6</v>
+      </c>
+      <c r="C5" t="s" s="8">
         <v>11</v>
       </c>
-      <c r="B6" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="G6" s="8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="8" t="s">
+      <c r="D5" t="s" s="8">
+        <v>8</v>
+      </c>
+      <c r="E5" t="s" s="8">
+        <v>8</v>
+      </c>
+      <c r="F5" t="s" s="8">
+        <v>8</v>
+      </c>
+      <c r="G5" t="s" s="8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" ht="20.05" customHeight="1">
+      <c r="A6" t="s" s="8">
         <v>12</v>
       </c>
-      <c r="B7" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="8" t="s">
+      <c r="B6" t="s" s="8">
+        <v>6</v>
+      </c>
+      <c r="C6" t="s" s="9">
+        <v>7</v>
+      </c>
+      <c r="D6" t="s" s="8">
+        <v>8</v>
+      </c>
+      <c r="E6" t="s" s="9">
+        <v>7</v>
+      </c>
+      <c r="F6" t="s" s="8">
+        <v>8</v>
+      </c>
+      <c r="G6" t="s" s="8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" ht="20.05" customHeight="1">
+      <c r="A7" t="s" s="8">
         <v>13</v>
       </c>
-      <c r="B8" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="G8" s="8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="8" t="s">
+      <c r="B7" t="s" s="8">
+        <v>6</v>
+      </c>
+      <c r="C7" t="s" s="9">
+        <v>7</v>
+      </c>
+      <c r="D7" t="s" s="8">
+        <v>8</v>
+      </c>
+      <c r="E7" t="s" s="9">
+        <v>7</v>
+      </c>
+      <c r="F7" t="s" s="8">
+        <v>8</v>
+      </c>
+      <c r="G7" t="s" s="8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" ht="20.05" customHeight="1">
+      <c r="A8" t="s" s="8">
         <v>14</v>
       </c>
-      <c r="B9" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="G9" s="8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="8" t="s">
+      <c r="B8" t="s" s="8">
+        <v>6</v>
+      </c>
+      <c r="C8" t="s" s="9">
+        <v>7</v>
+      </c>
+      <c r="D8" t="s" s="8">
+        <v>8</v>
+      </c>
+      <c r="E8" t="s" s="9">
+        <v>7</v>
+      </c>
+      <c r="F8" t="s" s="8">
+        <v>8</v>
+      </c>
+      <c r="G8" t="s" s="8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" ht="20.05" customHeight="1">
+      <c r="A9" t="s" s="8">
         <v>15</v>
       </c>
-      <c r="B10" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="G10" s="8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="8" t="s">
+      <c r="B9" t="s" s="8">
+        <v>6</v>
+      </c>
+      <c r="C9" t="s" s="8">
+        <v>6</v>
+      </c>
+      <c r="D9" t="s" s="8">
+        <v>8</v>
+      </c>
+      <c r="E9" t="s" s="8">
+        <v>8</v>
+      </c>
+      <c r="F9" t="s" s="8">
+        <v>8</v>
+      </c>
+      <c r="G9" t="s" s="8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" ht="20.05" customHeight="1">
+      <c r="A10" t="s" s="8">
         <v>16</v>
       </c>
-      <c r="B11" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="G11" s="8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="8" t="s">
+      <c r="B10" t="s" s="8">
+        <v>6</v>
+      </c>
+      <c r="C10" t="s" s="8">
+        <v>6</v>
+      </c>
+      <c r="D10" t="s" s="8">
+        <v>8</v>
+      </c>
+      <c r="E10" t="s" s="8">
+        <v>8</v>
+      </c>
+      <c r="F10" t="s" s="8">
+        <v>8</v>
+      </c>
+      <c r="G10" t="s" s="8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" ht="20.05" customHeight="1">
+      <c r="A11" t="s" s="8">
         <v>17</v>
       </c>
-      <c r="B12" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="F12" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="G12" s="9" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="8" t="s">
+      <c r="B11" t="s" s="8">
+        <v>6</v>
+      </c>
+      <c r="C11" t="s" s="8">
+        <v>6</v>
+      </c>
+      <c r="D11" t="s" s="8">
+        <v>8</v>
+      </c>
+      <c r="E11" t="s" s="8">
+        <v>8</v>
+      </c>
+      <c r="F11" t="s" s="8">
+        <v>8</v>
+      </c>
+      <c r="G11" t="s" s="8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" ht="20.05" customHeight="1">
+      <c r="A12" t="s" s="8">
         <v>18</v>
       </c>
-      <c r="B13" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E13" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="F13" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="G13" s="8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="8" t="s">
+      <c r="B12" t="s" s="8">
+        <v>6</v>
+      </c>
+      <c r="C12" t="s" s="9">
+        <v>7</v>
+      </c>
+      <c r="D12" t="s" s="8">
+        <v>8</v>
+      </c>
+      <c r="E12" t="s" s="9">
+        <v>7</v>
+      </c>
+      <c r="F12" t="s" s="8">
+        <v>8</v>
+      </c>
+      <c r="G12" t="s" s="9">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" ht="44.05" customHeight="1">
+      <c r="A13" t="s" s="8">
         <v>19</v>
       </c>
-      <c r="B14" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E14" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="G14" s="8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="8" t="s">
+      <c r="B13" t="s" s="8">
+        <v>6</v>
+      </c>
+      <c r="C13" t="s" s="9">
+        <v>7</v>
+      </c>
+      <c r="D13" t="s" s="8">
+        <v>8</v>
+      </c>
+      <c r="E13" t="s" s="9">
+        <v>7</v>
+      </c>
+      <c r="F13" t="s" s="8">
+        <v>8</v>
+      </c>
+      <c r="G13" t="s" s="9">
         <v>20</v>
       </c>
-      <c r="B15" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="D15" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="G15" s="8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="8" t="s">
+    </row>
+    <row r="14" ht="20.05" customHeight="1">
+      <c r="A14" t="s" s="8">
         <v>21</v>
       </c>
-      <c r="B16" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E16" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="G16" s="8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="8" t="s">
+      <c r="B14" t="s" s="8">
+        <v>6</v>
+      </c>
+      <c r="C14" t="s" s="8">
+        <v>6</v>
+      </c>
+      <c r="D14" t="s" s="8">
+        <v>8</v>
+      </c>
+      <c r="E14" t="s" s="8">
+        <v>8</v>
+      </c>
+      <c r="F14" t="s" s="8">
+        <v>8</v>
+      </c>
+      <c r="G14" t="s" s="8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" ht="20.05" customHeight="1">
+      <c r="A15" t="s" s="8">
         <v>22</v>
       </c>
-      <c r="B17" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="D17" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E17" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="F17" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="G17" s="8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A18" s="8" t="s">
+      <c r="B15" t="s" s="8">
+        <v>6</v>
+      </c>
+      <c r="C15" t="s" s="8">
+        <v>6</v>
+      </c>
+      <c r="D15" t="s" s="8">
+        <v>8</v>
+      </c>
+      <c r="E15" t="s" s="8">
+        <v>8</v>
+      </c>
+      <c r="F15" t="s" s="8">
+        <v>8</v>
+      </c>
+      <c r="G15" t="s" s="8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" ht="20.05" customHeight="1">
+      <c r="A16" t="s" s="8">
         <v>23</v>
       </c>
-      <c r="B18" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C18" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="D18" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E18" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="F18" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="G18" s="8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="8" t="s">
+      <c r="B16" t="s" s="8">
+        <v>6</v>
+      </c>
+      <c r="C16" t="s" s="8">
+        <v>6</v>
+      </c>
+      <c r="D16" t="s" s="8">
+        <v>8</v>
+      </c>
+      <c r="E16" t="s" s="8">
+        <v>8</v>
+      </c>
+      <c r="F16" t="s" s="8">
+        <v>8</v>
+      </c>
+      <c r="G16" t="s" s="8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" ht="20.05" customHeight="1">
+      <c r="A17" t="s" s="8">
         <v>24</v>
       </c>
-      <c r="B19" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C19" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E19" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="F19" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="G19" s="8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="8" t="s">
+      <c r="B17" t="s" s="8">
+        <v>6</v>
+      </c>
+      <c r="C17" t="s" s="9">
+        <v>7</v>
+      </c>
+      <c r="D17" t="s" s="8">
+        <v>8</v>
+      </c>
+      <c r="E17" t="s" s="9">
+        <v>7</v>
+      </c>
+      <c r="F17" t="s" s="8">
+        <v>8</v>
+      </c>
+      <c r="G17" t="s" s="8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" ht="20.05" customHeight="1">
+      <c r="A18" t="s" s="8">
         <v>25</v>
       </c>
-      <c r="B20" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C20" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="D20" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E20" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="G20" s="8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A21" s="8" t="s">
+      <c r="B18" t="s" s="8">
+        <v>6</v>
+      </c>
+      <c r="C18" t="s" s="9">
+        <v>7</v>
+      </c>
+      <c r="D18" t="s" s="8">
+        <v>8</v>
+      </c>
+      <c r="E18" t="s" s="9">
+        <v>7</v>
+      </c>
+      <c r="F18" t="s" s="8">
+        <v>8</v>
+      </c>
+      <c r="G18" t="s" s="8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" ht="20.05" customHeight="1">
+      <c r="A19" t="s" s="8">
         <v>26</v>
       </c>
-      <c r="B21" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C21" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="D21" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E21" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="F21" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="G21" s="8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A22" s="8" t="s">
+      <c r="B19" t="s" s="8">
+        <v>6</v>
+      </c>
+      <c r="C19" t="s" s="9">
+        <v>7</v>
+      </c>
+      <c r="D19" t="s" s="8">
+        <v>8</v>
+      </c>
+      <c r="E19" t="s" s="9">
+        <v>7</v>
+      </c>
+      <c r="F19" t="s" s="8">
+        <v>8</v>
+      </c>
+      <c r="G19" t="s" s="8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20" ht="20.05" customHeight="1">
+      <c r="A20" t="s" s="8">
         <v>27</v>
       </c>
-      <c r="B22" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C22" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="D22" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E22" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F22" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="G22" s="8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A23" s="8" t="s">
+      <c r="B20" t="s" s="8">
+        <v>6</v>
+      </c>
+      <c r="C20" t="s" s="8">
+        <v>6</v>
+      </c>
+      <c r="D20" t="s" s="8">
+        <v>8</v>
+      </c>
+      <c r="E20" t="s" s="8">
+        <v>8</v>
+      </c>
+      <c r="F20" t="s" s="8">
+        <v>8</v>
+      </c>
+      <c r="G20" t="s" s="8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" ht="20.05" customHeight="1">
+      <c r="A21" t="s" s="8">
         <v>28</v>
       </c>
-      <c r="B23" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C23" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="D23" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E23" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F23" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="G23" s="8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A24" s="8" t="s">
+      <c r="B21" t="s" s="8">
+        <v>6</v>
+      </c>
+      <c r="C21" t="s" s="9">
+        <v>7</v>
+      </c>
+      <c r="D21" t="s" s="8">
+        <v>8</v>
+      </c>
+      <c r="E21" t="s" s="9">
+        <v>7</v>
+      </c>
+      <c r="F21" t="s" s="8">
+        <v>8</v>
+      </c>
+      <c r="G21" t="s" s="8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" ht="20.05" customHeight="1">
+      <c r="A22" t="s" s="8">
         <v>29</v>
       </c>
-      <c r="B24" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C24" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="D24" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E24" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F24" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="G24" s="8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="8" t="s">
+      <c r="B22" t="s" s="8">
+        <v>6</v>
+      </c>
+      <c r="C22" t="s" s="8">
+        <v>6</v>
+      </c>
+      <c r="D22" t="s" s="8">
+        <v>8</v>
+      </c>
+      <c r="E22" t="s" s="8">
+        <v>8</v>
+      </c>
+      <c r="F22" t="s" s="8">
+        <v>8</v>
+      </c>
+      <c r="G22" t="s" s="8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" ht="20.05" customHeight="1">
+      <c r="A23" t="s" s="8">
         <v>30</v>
       </c>
-      <c r="B25" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C25" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="D25" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E25" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F25" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="G25" s="8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A26" s="8" t="s">
+      <c r="B23" t="s" s="8">
+        <v>6</v>
+      </c>
+      <c r="C23" t="s" s="8">
+        <v>6</v>
+      </c>
+      <c r="D23" t="s" s="8">
+        <v>8</v>
+      </c>
+      <c r="E23" t="s" s="8">
+        <v>8</v>
+      </c>
+      <c r="F23" t="s" s="8">
+        <v>8</v>
+      </c>
+      <c r="G23" t="s" s="8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24" ht="20.05" customHeight="1">
+      <c r="A24" t="s" s="8">
         <v>31</v>
       </c>
-      <c r="B26" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C26" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="D26" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E26" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F26" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="G26" s="8" t="s">
+      <c r="B24" t="s" s="8">
+        <v>6</v>
+      </c>
+      <c r="C24" t="s" s="8">
+        <v>6</v>
+      </c>
+      <c r="D24" t="s" s="8">
+        <v>8</v>
+      </c>
+      <c r="E24" t="s" s="8">
+        <v>8</v>
+      </c>
+      <c r="F24" t="s" s="8">
+        <v>8</v>
+      </c>
+      <c r="G24" t="s" s="8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25" ht="20.05" customHeight="1">
+      <c r="A25" t="s" s="8">
+        <v>32</v>
+      </c>
+      <c r="B25" t="s" s="8">
+        <v>6</v>
+      </c>
+      <c r="C25" t="s" s="8">
+        <v>6</v>
+      </c>
+      <c r="D25" t="s" s="8">
+        <v>8</v>
+      </c>
+      <c r="E25" t="s" s="8">
+        <v>8</v>
+      </c>
+      <c r="F25" t="s" s="8">
+        <v>8</v>
+      </c>
+      <c r="G25" t="s" s="8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26" ht="20.05" customHeight="1">
+      <c r="A26" t="s" s="8">
+        <v>33</v>
+      </c>
+      <c r="B26" t="s" s="8">
+        <v>6</v>
+      </c>
+      <c r="C26" t="s" s="8">
+        <v>6</v>
+      </c>
+      <c r="D26" t="s" s="8">
+        <v>8</v>
+      </c>
+      <c r="E26" t="s" s="8">
+        <v>8</v>
+      </c>
+      <c r="F26" t="s" s="8">
+        <v>8</v>
+      </c>
+      <c r="G26" t="s" s="8">
         <v>8</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.27777800000000002" footer="0.27777800000000002"/>
-  <pageSetup scale="72" orientation="portrait"/>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.277778" footer="0.277778"/>
+  <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="72" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>
   <headerFooter>
     <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
   </headerFooter>

--- a/form-control-tests.xlsx
+++ b/form-control-tests.xlsx
@@ -1,17 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10917"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/russweakley-intopia/Desktop/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB7D762B-D0D1-5D4C-B66A-378D370385F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="40" windowWidth="15960" windowHeight="18080"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="15960" windowHeight="18080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet 1-1" sheetId="1" r:id="rId4"/>
+    <sheet name="macOS-Chrome" sheetId="2" r:id="rId1"/>
+    <sheet name="macOS-Firefox" sheetId="3" r:id="rId2"/>
+    <sheet name="macOS-Safari" sheetId="4" r:id="rId3"/>
+    <sheet name="Windows-Chrome" sheetId="5" r:id="rId4"/>
+    <sheet name="Windows-Firefox" sheetId="6" r:id="rId5"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="905" uniqueCount="43">
+  <si>
+    <t>MacOS Chrome</t>
+  </si>
   <si>
     <t>Raw</t>
   </si>
@@ -31,22 +47,22 @@
     <t>&lt;button&gt;</t>
   </si>
   <si>
-    <t>Yes</t>
+    <t>Blue ring</t>
   </si>
   <si>
     <t>No</t>
   </si>
   <si>
-    <t>Red</t>
+    <t>Red outline</t>
+  </si>
+  <si>
+    <t>Purple outline</t>
   </si>
   <si>
     <t>&lt;textarea&gt;</t>
   </si>
   <si>
     <t>&lt;select&gt;</t>
-  </si>
-  <si>
-    <t>Yes for all. No for Firefox Windows</t>
   </si>
   <si>
     <t>&lt;input type="button"&gt;</t>
@@ -71,9 +87,6 @@
   </si>
   <si>
     <t>&lt;input type="image"&gt;</t>
-  </si>
-  <si>
-    <t>No for all. Red for Chrome and Firefox  Windows</t>
   </si>
   <si>
     <t>&lt;input type="month"&gt;</t>
@@ -114,33 +127,52 @@
   <si>
     <t>&lt;input type="week"&gt;</t>
   </si>
+  <si>
+    <t>MacOS Firefox</t>
+  </si>
+  <si>
+    <t>MacOS Safari</t>
+  </si>
+  <si>
+    <t>Does not receive focus</t>
+  </si>
+  <si>
+    <t>Focus moves into each date field but not the overall component</t>
+  </si>
+  <si>
+    <t>Cannot click on the component, just aspects of the date</t>
+  </si>
+  <si>
+    <t>Focus moved into each field but overall component still receives Purple outline</t>
+  </si>
+  <si>
+    <t>Windows Chrome</t>
+  </si>
+  <si>
+    <t>Black not blue ring</t>
+  </si>
+  <si>
+    <t>Windows Firefox</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="0" formatCode="General"/>
-  </numFmts>
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color indexed="8"/>
       <name val="Helvetica Neue"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color indexed="8"/>
-      <name val="Helvetica Neue"/>
-    </font>
-    <font>
-      <b val="1"/>
+      <b/>
       <sz val="10"/>
       <color indexed="8"/>
       <name val="Helvetica Neue"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -149,13 +181,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor indexed="9"/>
+        <fgColor indexed="12"/>
         <bgColor auto="1"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor indexed="12"/>
+        <fgColor indexed="15"/>
+        <bgColor auto="1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="16"/>
         <bgColor auto="1"/>
       </patternFill>
     </fill>
@@ -170,84 +208,84 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="10"/>
+        <color indexed="13"/>
       </left>
       <right style="thin">
-        <color indexed="10"/>
+        <color indexed="13"/>
       </right>
       <top style="thin">
-        <color indexed="10"/>
+        <color indexed="13"/>
       </top>
       <bottom style="thin">
-        <color indexed="10"/>
+        <color indexed="13"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="10"/>
+        <color indexed="13"/>
       </left>
       <right style="thin">
-        <color indexed="10"/>
+        <color indexed="13"/>
       </right>
       <top style="thin">
-        <color indexed="10"/>
+        <color indexed="13"/>
       </top>
       <bottom style="thin">
-        <color indexed="11"/>
+        <color indexed="14"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="10"/>
+        <color indexed="13"/>
       </left>
       <right style="thin">
-        <color indexed="10"/>
+        <color indexed="13"/>
       </right>
       <top style="thin">
-        <color indexed="11"/>
+        <color indexed="14"/>
       </top>
       <bottom style="thin">
-        <color indexed="10"/>
+        <color indexed="13"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="10">
-    <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -258,26 +296,85 @@
   <tableStyles count="0"/>
   <colors>
     <indexedColors>
-      <rgbColor rgb="ff000000"/>
-      <rgbColor rgb="ffffffff"/>
-      <rgbColor rgb="ffff0000"/>
-      <rgbColor rgb="ff00ff00"/>
-      <rgbColor rgb="ff0000ff"/>
-      <rgbColor rgb="ffffff00"/>
-      <rgbColor rgb="ffff00ff"/>
-      <rgbColor rgb="ff00ffff"/>
-      <rgbColor rgb="ff000000"/>
-      <rgbColor rgb="ffbdc0bf"/>
-      <rgbColor rgb="ffa5a5a5"/>
-      <rgbColor rgb="ff3f3f3f"/>
-      <rgbColor rgb="ffff94ca"/>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FF00FF00"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FF5E88B1"/>
+      <rgbColor rgb="FFEEF3F4"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FFBDC0BF"/>
+      <rgbColor rgb="FFA5A5A5"/>
+      <rgbColor rgb="FF3F3F3F"/>
+      <rgbColor rgb="FFFF94CA"/>
+      <rgbColor rgb="FFFFF056"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Blank">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Blank">
   <a:themeElements>
     <a:clrScheme name="Blank">
       <a:dk1>
@@ -476,7 +573,7 @@
         <a:effectLst/>
         <a:sp3d/>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="50800" tIns="50800" rIns="50800" bIns="50800" numCol="1" spcCol="38100" rtlCol="0" anchor="ctr" upright="0">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="50800" tIns="50800" rIns="50800" bIns="50800" numCol="1" spcCol="38100" rtlCol="0" anchor="ctr">
         <a:spAutoFit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -494,7 +591,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1200" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1200" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -523,7 +620,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -548,7 +645,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -573,7 +670,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -598,7 +695,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -623,7 +720,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -648,7 +745,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -673,7 +770,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -698,7 +795,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -723,7 +820,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -736,9 +833,15 @@
         </a:lvl9pPr>
       </a:lstStyle>
       <a:style>
-        <a:lnRef idx="0"/>
-        <a:fillRef idx="0"/>
-        <a:effectRef idx="0"/>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
         <a:fontRef idx="none"/>
       </a:style>
     </a:spDef>
@@ -755,7 +858,7 @@
         <a:effectLst/>
         <a:sp3d/>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="91439" tIns="45719" rIns="91439" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="t" upright="0">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="91439" tIns="45719" rIns="91439" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="t">
         <a:noAutofit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -773,7 +876,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -798,7 +901,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -823,7 +926,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -848,7 +951,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -873,7 +976,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -898,7 +1001,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -923,7 +1026,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -948,7 +1051,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -973,7 +1076,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -998,7 +1101,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1011,9 +1114,15 @@
         </a:lvl9pPr>
       </a:lstStyle>
       <a:style>
-        <a:lnRef idx="0"/>
-        <a:fillRef idx="0"/>
-        <a:effectRef idx="0"/>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
         <a:fontRef idx="none"/>
       </a:style>
     </a:lnDef>
@@ -1027,7 +1136,7 @@
         <a:effectLst/>
         <a:sp3d/>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="50800" tIns="50800" rIns="50800" bIns="50800" numCol="1" spcCol="38100" rtlCol="0" anchor="t" upright="0">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="50800" tIns="50800" rIns="50800" bIns="50800" numCol="1" spcCol="38100" rtlCol="0" anchor="t">
         <a:spAutoFit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -1045,7 +1154,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1100" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1100" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1074,7 +1183,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1099,7 +1208,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1124,7 +1233,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1149,7 +1258,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1174,7 +1283,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1199,7 +1308,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1224,7 +1333,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1249,7 +1358,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1274,7 +1383,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1287,624 +1396,3103 @@
         </a:lvl9pPr>
       </a:lstStyle>
       <a:style>
-        <a:lnRef idx="0"/>
-        <a:fillRef idx="0"/>
-        <a:effectRef idx="0"/>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
         <a:fontRef idx="none"/>
       </a:style>
     </a:txDef>
   </a:objectDefaults>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:G26"/>
-  <sheetFormatPr defaultColWidth="16.3333" defaultRowHeight="19.9" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="16.33203125" defaultRowHeight="20" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="31.5625" style="1" customWidth="1"/>
-    <col min="2" max="6" width="16.3516" style="1" customWidth="1"/>
-    <col min="7" max="7" width="16.1875" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="16.3516" style="1" customWidth="1"/>
+    <col min="1" max="1" width="31.5" style="1" customWidth="1"/>
+    <col min="2" max="6" width="16.33203125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.1640625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="16.33203125" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="16.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20.05" customHeight="1">
-      <c r="A1" s="2"/>
-      <c r="B1" t="s" s="3">
+    <row r="1" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C1" t="s" s="3">
-        <v>0</v>
-      </c>
-      <c r="D1" t="s" s="3">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="E1" t="s" s="3">
+      <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F1" t="s" s="3">
+      <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="G1" t="s" s="3">
+      <c r="E1" s="2" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" ht="32.25" customHeight="1">
-      <c r="A2" s="4"/>
-      <c r="B2" t="s" s="5">
+      <c r="F1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C2" t="s" s="5">
+      <c r="G1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="32.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="3"/>
+      <c r="B2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D2" t="s" s="5">
+      <c r="C2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A4" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A5" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A7" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A8" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A9" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A10" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A11" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A12" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A13" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A14" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A15" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A16" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A17" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A18" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G18" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A19" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A20" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A21" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G21" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A22" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G22" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A23" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F23" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G23" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A24" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G24" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A25" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G25" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A26" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G26" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.27777800000000002" footer="0.27777800000000002"/>
+  <pageSetup scale="72" orientation="portrait"/>
+  <headerFooter>
+    <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:G26"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="16.33203125" defaultRowHeight="20" customHeight="1" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="1" max="1" width="31.5" style="1" customWidth="1"/>
+    <col min="2" max="6" width="16.33203125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.1640625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="16.33203125" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="16.33203125" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E2" t="s" s="5">
+      <c r="G1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="32.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="3"/>
+      <c r="B2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F2" t="s" s="5">
+      <c r="C2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A4" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A5" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A7" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A8" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A9" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A10" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A11" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A12" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A13" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A14" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A15" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A16" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A17" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A18" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G18" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A19" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A20" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A21" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G21" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A22" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G22" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A23" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F23" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G23" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A24" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G24" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A25" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G25" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A26" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G26" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.27777800000000002" footer="0.27777800000000002"/>
+  <pageSetup scale="72" orientation="portrait"/>
+  <headerFooter>
+    <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:G26"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="16.33203125" defaultRowHeight="20" customHeight="1" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="1" max="1" width="31.5" style="1" customWidth="1"/>
+    <col min="2" max="2" width="18.5" style="1" customWidth="1"/>
+    <col min="3" max="6" width="16.33203125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.1640625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="16.33203125" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="16.33203125" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="G2" t="s" s="5">
+      <c r="G1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="32.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="3"/>
+      <c r="B2" s="4" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="3" ht="20.25" customHeight="1">
-      <c r="A3" t="s" s="6">
+      <c r="C2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B3" t="s" s="6">
+      <c r="D2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C3" t="s" s="7">
-        <v>7</v>
-      </c>
-      <c r="D3" t="s" s="6">
-        <v>8</v>
-      </c>
-      <c r="E3" t="s" s="7">
-        <v>7</v>
-      </c>
-      <c r="F3" t="s" s="6">
-        <v>8</v>
-      </c>
-      <c r="G3" t="s" s="6">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" ht="20.05" customHeight="1">
-      <c r="A4" t="s" s="8">
-        <v>9</v>
-      </c>
-      <c r="B4" t="s" s="8">
+      <c r="B3" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A4" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A5" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A7" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="32" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A8" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="68" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A9" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="68" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A10" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A11" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A12" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A13" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A14" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A15" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A16" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A17" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G17" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A18" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G18" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A19" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G19" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A20" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A21" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G21" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A22" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G22" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A23" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F23" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G23" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="68" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A24" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D24" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="E24" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="F24" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="G24" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A25" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G25" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A26" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G26" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.27777800000000002" footer="0.27777800000000002"/>
+  <pageSetup scale="72" orientation="portrait"/>
+  <headerFooter>
+    <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:G26"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="16.33203125" defaultRowHeight="20" customHeight="1" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="1" max="1" width="31.5" style="1" customWidth="1"/>
+    <col min="2" max="6" width="16.33203125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.1640625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="16.33203125" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="16.33203125" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="32.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="3"/>
+      <c r="B2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C4" t="s" s="8">
+      <c r="B3" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A4" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A5" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A7" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A8" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A9" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A10" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A11" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A12" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A13" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A14" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A15" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A16" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A17" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A18" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G18" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A19" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A20" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A21" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G21" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A22" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G22" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A23" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F23" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G23" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A24" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G24" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A25" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G25" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A26" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G26" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.27777800000000002" footer="0.27777800000000002"/>
+  <pageSetup scale="72" orientation="portrait"/>
+  <headerFooter>
+    <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:G26"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="16.33203125" defaultRowHeight="20" customHeight="1" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="1" max="1" width="31.5" style="1" customWidth="1"/>
+    <col min="2" max="6" width="16.33203125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.1640625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="16.33203125" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="16.33203125" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="32.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="3"/>
+      <c r="B2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D4" t="s" s="8">
-        <v>8</v>
-      </c>
-      <c r="E4" t="s" s="8">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s" s="8">
-        <v>8</v>
-      </c>
-      <c r="G4" t="s" s="8">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" ht="32.05" customHeight="1">
-      <c r="A5" t="s" s="8">
-        <v>10</v>
-      </c>
-      <c r="B5" t="s" s="8">
-        <v>6</v>
-      </c>
-      <c r="C5" t="s" s="8">
+      <c r="B3" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A4" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D5" t="s" s="8">
-        <v>8</v>
-      </c>
-      <c r="E5" t="s" s="8">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s" s="8">
-        <v>8</v>
-      </c>
-      <c r="G5" t="s" s="8">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" ht="20.05" customHeight="1">
-      <c r="A6" t="s" s="8">
+      <c r="B4" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A5" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B6" t="s" s="8">
-        <v>6</v>
-      </c>
-      <c r="C6" t="s" s="9">
-        <v>7</v>
-      </c>
-      <c r="D6" t="s" s="8">
-        <v>8</v>
-      </c>
-      <c r="E6" t="s" s="9">
-        <v>7</v>
-      </c>
-      <c r="F6" t="s" s="8">
-        <v>8</v>
-      </c>
-      <c r="G6" t="s" s="8">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" ht="20.05" customHeight="1">
-      <c r="A7" t="s" s="8">
+      <c r="B5" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B7" t="s" s="8">
-        <v>6</v>
-      </c>
-      <c r="C7" t="s" s="9">
-        <v>7</v>
-      </c>
-      <c r="D7" t="s" s="8">
-        <v>8</v>
-      </c>
-      <c r="E7" t="s" s="9">
-        <v>7</v>
-      </c>
-      <c r="F7" t="s" s="8">
-        <v>8</v>
-      </c>
-      <c r="G7" t="s" s="8">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" ht="20.05" customHeight="1">
-      <c r="A8" t="s" s="8">
+      <c r="B6" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A7" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="B8" t="s" s="8">
-        <v>6</v>
-      </c>
-      <c r="C8" t="s" s="9">
-        <v>7</v>
-      </c>
-      <c r="D8" t="s" s="8">
-        <v>8</v>
-      </c>
-      <c r="E8" t="s" s="9">
-        <v>7</v>
-      </c>
-      <c r="F8" t="s" s="8">
-        <v>8</v>
-      </c>
-      <c r="G8" t="s" s="8">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" ht="20.05" customHeight="1">
-      <c r="A9" t="s" s="8">
+      <c r="B7" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A8" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="B9" t="s" s="8">
-        <v>6</v>
-      </c>
-      <c r="C9" t="s" s="8">
-        <v>6</v>
-      </c>
-      <c r="D9" t="s" s="8">
-        <v>8</v>
-      </c>
-      <c r="E9" t="s" s="8">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s" s="8">
-        <v>8</v>
-      </c>
-      <c r="G9" t="s" s="8">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" ht="20.05" customHeight="1">
-      <c r="A10" t="s" s="8">
+      <c r="B8" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A9" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B10" t="s" s="8">
-        <v>6</v>
-      </c>
-      <c r="C10" t="s" s="8">
-        <v>6</v>
-      </c>
-      <c r="D10" t="s" s="8">
-        <v>8</v>
-      </c>
-      <c r="E10" t="s" s="8">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s" s="8">
-        <v>8</v>
-      </c>
-      <c r="G10" t="s" s="8">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" ht="20.05" customHeight="1">
-      <c r="A11" t="s" s="8">
+      <c r="B9" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A10" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="B11" t="s" s="8">
-        <v>6</v>
-      </c>
-      <c r="C11" t="s" s="8">
-        <v>6</v>
-      </c>
-      <c r="D11" t="s" s="8">
-        <v>8</v>
-      </c>
-      <c r="E11" t="s" s="8">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s" s="8">
-        <v>8</v>
-      </c>
-      <c r="G11" t="s" s="8">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12" ht="20.05" customHeight="1">
-      <c r="A12" t="s" s="8">
+      <c r="B10" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A11" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="B12" t="s" s="8">
-        <v>6</v>
-      </c>
-      <c r="C12" t="s" s="9">
-        <v>7</v>
-      </c>
-      <c r="D12" t="s" s="8">
-        <v>8</v>
-      </c>
-      <c r="E12" t="s" s="9">
-        <v>7</v>
-      </c>
-      <c r="F12" t="s" s="8">
-        <v>8</v>
-      </c>
-      <c r="G12" t="s" s="9">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="13" ht="44.05" customHeight="1">
-      <c r="A13" t="s" s="8">
+      <c r="B11" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A12" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="B13" t="s" s="8">
-        <v>6</v>
-      </c>
-      <c r="C13" t="s" s="9">
-        <v>7</v>
-      </c>
-      <c r="D13" t="s" s="8">
-        <v>8</v>
-      </c>
-      <c r="E13" t="s" s="9">
-        <v>7</v>
-      </c>
-      <c r="F13" t="s" s="8">
-        <v>8</v>
-      </c>
-      <c r="G13" t="s" s="9">
+      <c r="B12" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A13" s="7" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="14" ht="20.05" customHeight="1">
-      <c r="A14" t="s" s="8">
+      <c r="B13" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A14" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B14" t="s" s="8">
-        <v>6</v>
-      </c>
-      <c r="C14" t="s" s="8">
-        <v>6</v>
-      </c>
-      <c r="D14" t="s" s="8">
-        <v>8</v>
-      </c>
-      <c r="E14" t="s" s="8">
-        <v>8</v>
-      </c>
-      <c r="F14" t="s" s="8">
-        <v>8</v>
-      </c>
-      <c r="G14" t="s" s="8">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="15" ht="20.05" customHeight="1">
-      <c r="A15" t="s" s="8">
+      <c r="B14" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A15" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B15" t="s" s="8">
-        <v>6</v>
-      </c>
-      <c r="C15" t="s" s="8">
-        <v>6</v>
-      </c>
-      <c r="D15" t="s" s="8">
-        <v>8</v>
-      </c>
-      <c r="E15" t="s" s="8">
-        <v>8</v>
-      </c>
-      <c r="F15" t="s" s="8">
-        <v>8</v>
-      </c>
-      <c r="G15" t="s" s="8">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="16" ht="20.05" customHeight="1">
-      <c r="A16" t="s" s="8">
+      <c r="B15" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A16" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="B16" t="s" s="8">
-        <v>6</v>
-      </c>
-      <c r="C16" t="s" s="8">
-        <v>6</v>
-      </c>
-      <c r="D16" t="s" s="8">
-        <v>8</v>
-      </c>
-      <c r="E16" t="s" s="8">
-        <v>8</v>
-      </c>
-      <c r="F16" t="s" s="8">
-        <v>8</v>
-      </c>
-      <c r="G16" t="s" s="8">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="17" ht="20.05" customHeight="1">
-      <c r="A17" t="s" s="8">
+      <c r="B16" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A17" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="B17" t="s" s="8">
-        <v>6</v>
-      </c>
-      <c r="C17" t="s" s="9">
-        <v>7</v>
-      </c>
-      <c r="D17" t="s" s="8">
-        <v>8</v>
-      </c>
-      <c r="E17" t="s" s="9">
-        <v>7</v>
-      </c>
-      <c r="F17" t="s" s="8">
-        <v>8</v>
-      </c>
-      <c r="G17" t="s" s="8">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="18" ht="20.05" customHeight="1">
-      <c r="A18" t="s" s="8">
+      <c r="B17" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A18" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="B18" t="s" s="8">
-        <v>6</v>
-      </c>
-      <c r="C18" t="s" s="9">
-        <v>7</v>
-      </c>
-      <c r="D18" t="s" s="8">
-        <v>8</v>
-      </c>
-      <c r="E18" t="s" s="9">
-        <v>7</v>
-      </c>
-      <c r="F18" t="s" s="8">
-        <v>8</v>
-      </c>
-      <c r="G18" t="s" s="8">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="19" ht="20.05" customHeight="1">
-      <c r="A19" t="s" s="8">
+      <c r="B18" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G18" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A19" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="B19" t="s" s="8">
-        <v>6</v>
-      </c>
-      <c r="C19" t="s" s="9">
-        <v>7</v>
-      </c>
-      <c r="D19" t="s" s="8">
-        <v>8</v>
-      </c>
-      <c r="E19" t="s" s="9">
-        <v>7</v>
-      </c>
-      <c r="F19" t="s" s="8">
-        <v>8</v>
-      </c>
-      <c r="G19" t="s" s="8">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="20" ht="20.05" customHeight="1">
-      <c r="A20" t="s" s="8">
+      <c r="B19" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A20" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="B20" t="s" s="8">
-        <v>6</v>
-      </c>
-      <c r="C20" t="s" s="8">
-        <v>6</v>
-      </c>
-      <c r="D20" t="s" s="8">
-        <v>8</v>
-      </c>
-      <c r="E20" t="s" s="8">
-        <v>8</v>
-      </c>
-      <c r="F20" t="s" s="8">
-        <v>8</v>
-      </c>
-      <c r="G20" t="s" s="8">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="21" ht="20.05" customHeight="1">
-      <c r="A21" t="s" s="8">
+      <c r="B20" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A21" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="B21" t="s" s="8">
-        <v>6</v>
-      </c>
-      <c r="C21" t="s" s="9">
-        <v>7</v>
-      </c>
-      <c r="D21" t="s" s="8">
-        <v>8</v>
-      </c>
-      <c r="E21" t="s" s="9">
-        <v>7</v>
-      </c>
-      <c r="F21" t="s" s="8">
-        <v>8</v>
-      </c>
-      <c r="G21" t="s" s="8">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="22" ht="20.05" customHeight="1">
-      <c r="A22" t="s" s="8">
+      <c r="B21" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G21" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A22" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="B22" t="s" s="8">
-        <v>6</v>
-      </c>
-      <c r="C22" t="s" s="8">
-        <v>6</v>
-      </c>
-      <c r="D22" t="s" s="8">
-        <v>8</v>
-      </c>
-      <c r="E22" t="s" s="8">
-        <v>8</v>
-      </c>
-      <c r="F22" t="s" s="8">
-        <v>8</v>
-      </c>
-      <c r="G22" t="s" s="8">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="23" ht="20.05" customHeight="1">
-      <c r="A23" t="s" s="8">
+      <c r="B22" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G22" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A23" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="B23" t="s" s="8">
-        <v>6</v>
-      </c>
-      <c r="C23" t="s" s="8">
-        <v>6</v>
-      </c>
-      <c r="D23" t="s" s="8">
-        <v>8</v>
-      </c>
-      <c r="E23" t="s" s="8">
-        <v>8</v>
-      </c>
-      <c r="F23" t="s" s="8">
-        <v>8</v>
-      </c>
-      <c r="G23" t="s" s="8">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="24" ht="20.05" customHeight="1">
-      <c r="A24" t="s" s="8">
+      <c r="B23" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F23" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G23" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A24" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="B24" t="s" s="8">
-        <v>6</v>
-      </c>
-      <c r="C24" t="s" s="8">
-        <v>6</v>
-      </c>
-      <c r="D24" t="s" s="8">
-        <v>8</v>
-      </c>
-      <c r="E24" t="s" s="8">
-        <v>8</v>
-      </c>
-      <c r="F24" t="s" s="8">
-        <v>8</v>
-      </c>
-      <c r="G24" t="s" s="8">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="25" ht="20.05" customHeight="1">
-      <c r="A25" t="s" s="8">
+      <c r="B24" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G24" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A25" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="B25" t="s" s="8">
-        <v>6</v>
-      </c>
-      <c r="C25" t="s" s="8">
-        <v>6</v>
-      </c>
-      <c r="D25" t="s" s="8">
-        <v>8</v>
-      </c>
-      <c r="E25" t="s" s="8">
-        <v>8</v>
-      </c>
-      <c r="F25" t="s" s="8">
-        <v>8</v>
-      </c>
-      <c r="G25" t="s" s="8">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="26" ht="20.05" customHeight="1">
-      <c r="A26" t="s" s="8">
+      <c r="B25" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G25" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A26" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="B26" t="s" s="8">
-        <v>6</v>
-      </c>
-      <c r="C26" t="s" s="8">
-        <v>6</v>
-      </c>
-      <c r="D26" t="s" s="8">
-        <v>8</v>
-      </c>
-      <c r="E26" t="s" s="8">
-        <v>8</v>
-      </c>
-      <c r="F26" t="s" s="8">
-        <v>8</v>
-      </c>
-      <c r="G26" t="s" s="8">
-        <v>8</v>
+      <c r="B26" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G26" s="7" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.277778" footer="0.277778"/>
-  <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="72" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.27777800000000002" footer="0.27777800000000002"/>
+  <pageSetup scale="72" orientation="portrait"/>
   <headerFooter>
     <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
   </headerFooter>
